--- a/docs/PG2-1-01_単体テストケース・結果一覧表_担当者引継ぎ実行.xlsx
+++ b/docs/PG2-1-01_単体テストケース・結果一覧表_担当者引継ぎ実行.xlsx
@@ -139,25 +139,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="HandoverTestCases" displayName="HandoverTestCases" ref="A6:N84" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="14">
-    <x:tableColumn id="1" name="項番"/>
-    <x:tableColumn id="2" name="分類"/>
-    <x:tableColumn id="3" name="テスト項目"/>
-    <x:tableColumn id="4" name="区分"/>
-    <x:tableColumn id="5" name="前提・入力データ"/>
-    <x:tableColumn id="6" name="操作・確認手順"/>
-    <x:tableColumn id="7" name="予想結果"/>
-    <x:tableColumn id="8" name="設計根拠"/>
-    <x:tableColumn id="9" name="確認事項"/>
-    <x:tableColumn id="10" name="準備状況"/>
-    <x:tableColumn id="11" name="実施結果"/>
-    <x:tableColumn id="12" name="実施日"/>
-    <x:tableColumn id="13" name="実施者"/>
-    <x:tableColumn id="14" name="証跡・不具合番号"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</x:table>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="HandoverTestCases" displayName="HandoverTestCases" ref="A6:N86" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <tableColumns count="14">
+    <tableColumn id="1" name="項番"/>
+    <tableColumn id="2" name="分類"/>
+    <tableColumn id="3" name="テスト項目"/>
+    <tableColumn id="4" name="区分"/>
+    <tableColumn id="5" name="前提・入力データ"/>
+    <tableColumn id="6" name="操作・確認手順"/>
+    <tableColumn id="7" name="予想結果"/>
+    <tableColumn id="8" name="設計根拠"/>
+    <tableColumn id="9" name="確認事項"/>
+    <tableColumn id="10" name="準備状況"/>
+    <tableColumn id="11" name="実施結果"/>
+    <tableColumn id="12" name="実施日"/>
+    <tableColumn id="13" name="実施者"/>
+    <tableColumn id="14" name="証跡・不具合番号"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -409,8 +409,10 @@
       <c r="N2" s="4"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="3" t="str">
-        <v>BLMMGMGHANDOVER　作成日：2026-10-26　全78ケース（未実施）　黄色の実績欄はテスト実施時に記入。仕様確認待ちは「仕様確認事項」を参照。</v>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>BLMMGMGHANDOVER　作成日：2026-10-26　全80ケース（未実施）　黄色の実績欄はテスト実施時に記入。仕様確認待ちは「仕様確認事項」を参照。 改訂反映：2026-10-27。</t>
+        </is>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1552,8 +1554,10 @@
 元担当者の行を余分に残さず、他の担当者を変更しない。</t>
         </is>
       </c>
-      <c r="H26" s="9" t="str">
-        <v>更新仕様!A50:C67</v>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>更新仕様!A54,A74:C91</t>
+        </is>
       </c>
       <c r="I26" s="9" t="str"/>
       <c r="J26" s="9" t="str">
@@ -1603,8 +1607,10 @@
           <t xml:space="preserve">法人番号 9900000021001/担当者ID U0210011だけが法人番号 9900000021001/担当者ID U0210012となり、法人番号 9900000021002/担当者ID U0210011は変更しない。</t>
         </is>
       </c>
-      <c r="H27" s="3" t="str">
-        <v>更新仕様!A54</v>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>更新仕様!A78</t>
+        </is>
       </c>
       <c r="I27" s="3" t="str"/>
       <c r="J27" s="3" t="str">
@@ -1654,8 +1660,10 @@
           <t xml:space="preserve">法人番号 9900000022001/担当者ID U0220011だけが法人番号 9900000022001/担当者ID U0220012となり、法人番号 9900000022001/担当者ID U0220013は変更しない。</t>
         </is>
       </c>
-      <c r="H28" s="9" t="str">
-        <v>更新仕様!A54</v>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>更新仕様!A78</t>
+        </is>
       </c>
       <c r="I28" s="9" t="str"/>
       <c r="J28" s="9" t="str">
@@ -1705,8 +1713,10 @@
 更新仕様のSET句には組織IDがないため、正しい項目と要否の確定後に判定する。</t>
         </is>
       </c>
-      <c r="H29" s="3" t="str">
-        <v>内容!AV45:AV46、更新仕様!A50:C67</v>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>内容!AV45:AV46、更新仕様!A74:C91</t>
+        </is>
       </c>
       <c r="I29" s="3" t="str">
         <v>Q02</v>
@@ -1759,8 +1769,10 @@
 詳細フローとSQLへの反映を確認してから判定する。</t>
         </is>
       </c>
-      <c r="H30" s="9" t="str">
-        <v>概要!B13:B14、更新仕様!A50:C67</v>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>概要!B13:B14、更新仕様!A74:C91</t>
+        </is>
       </c>
       <c r="I30" s="9" t="str">
         <v>Q03</v>
@@ -1808,13 +1820,15 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">対象の営業担当引継情報を物理削除する。
-担当者・過去データを変更しない。
-削除済み行を完了更新しない。</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="str">
-        <v>内容!AV53:AV55、更新仕様!A79:B90</v>
+          <t>法人番号9900000025001の営業担当引継情報を削除する。
+引継元・引継先とも不在でも、該当法人だけを終了する。過去データの存在確認・更新、完了更新は行わない。
+後続法人がある場合は次の法人を処理する。</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>内容!AV53:AV55、更新仕様!A103:B114、2026-10-27ユーザー確認</t>
+        </is>
       </c>
       <c r="I31" s="3" t="str"/>
       <c r="J31" s="3" t="str">
@@ -1832,8 +1846,10 @@
       <c r="B32" s="9" t="str">
         <v>引継情報削除</v>
       </c>
-      <c r="C32" s="9" t="str">
-        <v>削除対象以外の予定を保持</v>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>元・先とも不在の予定削除と後続法人の処理</t>
+        </is>
       </c>
       <c r="D32" s="9" t="str">
         <v>正常系</v>
@@ -1863,12 +1879,15 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">法人番号 9900000026001の引継情報だけを削除し、法人番号 9900000026002を巻き込まない。
-SQL例には削除対象行の絞込みがないため、削除キーの確定が必要。</t>
-        </is>
-      </c>
-      <c r="H32" s="9" t="str">
-        <v>更新仕様!A79:B90</v>
+          <t>法人番号9900000026001の引継情報だけを削除する。削除直後は法人番号9900000026002の予定を保持する。
+続行後、法人番号9900000026002の担当者U0260013をU0260012へ引き継ぎ、引継情報の状態を0（完了）に更新し、実施日時を設定する。
+バッチ全体を終了しない。削除キーの設計SQLへの明記はQ04で引き続き確認する。</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>更新仕様!A103:B114、2026-10-27ユーザー確認</t>
+        </is>
       </c>
       <c r="I32" s="9" t="str">
         <v>Q04</v>
@@ -1916,12 +1935,16 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者存在判定を法人番号単位にするか確定して判定する。
-暫定案：法人番号 9900000027001の無効な予定だけを削除し法人番号 9900000027002/担当者ID U0270011を保持する。</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="str">
-        <v>内容!AV36:AV37、更新仕様!A54,A79</v>
+          <t>存在判定は法人番号と引継元担当者IDで行う。
+法人番号9900000027001の引継情報だけを削除し、その法人の処理を終了する。
+法人番号9900000027002の担当者U0270011を保持する。
+削除キーの設計SQLへの明記はQ04で引き続き確認する。</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>内容!AV36:AV37、更新仕様!A54,A103、2026-10-27ユーザー確認</t>
+        </is>
       </c>
       <c r="I33" s="3" t="str">
         <v>Q04</v>
@@ -1974,8 +1997,10 @@
 8テーブル（月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・建物マスタ・CN対策実施申込情報・建物情報）の組織を組織ID O0280011のまま保持し、予定を完了0にする。</t>
         </is>
       </c>
-      <c r="H34" s="9" t="str">
-        <v>内容!AV66:AV67、フロー図 処理6 N→10</v>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>内容!AV74:AV75、フロー図 処理7 N→11</t>
+        </is>
       </c>
       <c r="I34" s="9" t="str"/>
       <c r="J34" s="9" t="str">
@@ -2025,8 +2050,10 @@
 登録エラー3にしない。</t>
         </is>
       </c>
-      <c r="H35" s="3" t="str">
-        <v>フロー図 処理6 N→10</v>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>フロー図 処理7 N→11</t>
+        </is>
       </c>
       <c r="I35" s="3" t="str"/>
       <c r="J35" s="3" t="str">
@@ -2078,8 +2105,10 @@
 法人番号9900000030001の担当者をU0300012へ更新し、引継実施ステータス0（完了）と実施日時を確認する。</t>
         </is>
       </c>
-      <c r="H36" s="9" t="str">
-        <v>更新仕様!A99:D108,A168:C179,C268:C269</v>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>更新仕様!A147:D156,A216:C227,C316:C317</t>
+        </is>
       </c>
       <c r="I36" s="9" t="str"/>
       <c r="J36" s="9" t="str">
@@ -2131,8 +2160,10 @@
 月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・CN対策実施申込情報・建物情報の行を新規作成せず、行が存在しないことをエラーにしない。</t>
         </is>
       </c>
-      <c r="H37" s="3" t="str">
-        <v>内容!AV84:AV98</v>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>内容!AV92:AV106</t>
+        </is>
       </c>
       <c r="I37" s="3" t="str"/>
       <c r="J37" s="3" t="str">
@@ -2184,8 +2215,10 @@
 NULL許容・扱いを確定する。</t>
         </is>
       </c>
-      <c r="H38" s="9" t="str">
-        <v>内容!AV66:AV67</v>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>内容!AV74:AV75</t>
+        </is>
       </c>
       <c r="I38" s="9" t="str">
         <v>Q08</v>
@@ -2247,8 +2280,10 @@
 非対象3件と組織以外の業務項目を保持し、件数を増減させない。</t>
         </is>
       </c>
-      <c r="H39" s="3" t="str">
-        <v>更新仕様!A108,A179,B185:B192</v>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>更新仕様!A156,A227,B233:B240</t>
+        </is>
       </c>
       <c r="I39" s="3" t="str"/>
       <c r="J39" s="3" t="str">
@@ -2303,8 +2338,10 @@
 法人番号9900000034001の引継実施ステータスを0（完了）にする。</t>
         </is>
       </c>
-      <c r="H40" s="9" t="str">
-        <v>内容!AV84:AV98</v>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>内容!AV92:AV106</t>
+        </is>
       </c>
       <c r="I40" s="9" t="str"/>
       <c r="J40" s="9" t="str">
@@ -2364,8 +2401,10 @@
 非対象3件と組織以外の業務項目を保持し、件数を増減させない。</t>
         </is>
       </c>
-      <c r="H41" s="3" t="str">
-        <v>更新仕様!A108,A179,B195:B202</v>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>更新仕様!A156,A227,B243:B250</t>
+        </is>
       </c>
       <c r="I41" s="3" t="str"/>
       <c r="J41" s="3" t="str">
@@ -2420,8 +2459,10 @@
 法人番号9900000036001の引継実施ステータスを0（完了）にする。</t>
         </is>
       </c>
-      <c r="H42" s="9" t="str">
-        <v>内容!AV84:AV98</v>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>内容!AV92:AV106</t>
+        </is>
       </c>
       <c r="I42" s="9" t="str"/>
       <c r="J42" s="9" t="str">
@@ -2481,8 +2522,10 @@
 非対象3件と組織以外の業務項目を保持し、件数を増減させない。</t>
         </is>
       </c>
-      <c r="H43" s="3" t="str">
-        <v>更新仕様!A108,A179,B205:B212</v>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>更新仕様!A156,A227,B253:B260</t>
+        </is>
       </c>
       <c r="I43" s="3" t="str"/>
       <c r="J43" s="3" t="str">
@@ -2537,8 +2580,10 @@
 法人番号9900000038001の引継実施ステータスを0（完了）にする。</t>
         </is>
       </c>
-      <c r="H44" s="9" t="str">
-        <v>内容!AV84:AV98</v>
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>内容!AV92:AV106</t>
+        </is>
       </c>
       <c r="I44" s="9" t="str"/>
       <c r="J44" s="9" t="str">
@@ -2598,8 +2643,10 @@
 非対象3件と組織以外の業務項目を保持し、件数を増減させない。</t>
         </is>
       </c>
-      <c r="H45" s="3" t="str">
-        <v>更新仕様!A108,A179,B215:B222</v>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>更新仕様!A156,A227,B263:B270</t>
+        </is>
       </c>
       <c r="I45" s="3" t="str"/>
       <c r="J45" s="3" t="str">
@@ -2654,8 +2701,10 @@
 法人番号9900000040001の引継実施ステータスを0（完了）にする。</t>
         </is>
       </c>
-      <c r="H46" s="9" t="str">
-        <v>内容!AV84:AV98</v>
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>内容!AV92:AV106</t>
+        </is>
       </c>
       <c r="I46" s="9" t="str"/>
       <c r="J46" s="9" t="str">
@@ -2715,8 +2764,10 @@
 非対象3件と組織以外の業務項目を保持し、件数を増減させない。</t>
         </is>
       </c>
-      <c r="H47" s="3" t="str">
-        <v>更新仕様!A108,A179,B225:B232</v>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>更新仕様!A156,A227,B273:B280</t>
+        </is>
       </c>
       <c r="I47" s="3" t="str"/>
       <c r="J47" s="3" t="str">
@@ -2771,8 +2822,10 @@
 法人番号9900000042001の引継実施ステータスを0（完了）にする。</t>
         </is>
       </c>
-      <c r="H48" s="9" t="str">
-        <v>内容!AV84:AV98</v>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>内容!AV92:AV106</t>
+        </is>
       </c>
       <c r="I48" s="9" t="str"/>
       <c r="J48" s="9" t="str">
@@ -2831,8 +2884,10 @@
 同意書取得組織以外の業務項目と件数を保持する。</t>
         </is>
       </c>
-      <c r="H49" s="3" t="str">
-        <v>更新仕様!A108,A179,B235:B242</v>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>更新仕様!A156,A227,B283:B290</t>
+        </is>
       </c>
       <c r="I49" s="3" t="str"/>
       <c r="J49" s="3" t="str">
@@ -2892,8 +2947,10 @@
 非対象3件と組織以外の業務項目を保持し、件数を増減させない。</t>
         </is>
       </c>
-      <c r="H50" s="9" t="str">
-        <v>更新仕様!A108,A179,B244:B251</v>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>更新仕様!A156,A227,B292:B299</t>
+        </is>
       </c>
       <c r="I50" s="9" t="str"/>
       <c r="J50" s="9" t="str">
@@ -2948,8 +3005,10 @@
 法人番号9900000045001の引継実施ステータスを0（完了）にする。</t>
         </is>
       </c>
-      <c r="H51" s="3" t="str">
-        <v>内容!AV84:AV98</v>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>内容!AV92:AV106</t>
+        </is>
       </c>
       <c r="I51" s="3" t="str"/>
       <c r="J51" s="3" t="str">
@@ -3009,8 +3068,10 @@
 非対象3件と組織以外の業務項目を保持し、件数を増減させない。</t>
         </is>
       </c>
-      <c r="H52" s="9" t="str">
-        <v>更新仕様!A108,A179,B254:B261</v>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>更新仕様!A156,A227,B302:B309</t>
+        </is>
       </c>
       <c r="I52" s="9" t="str"/>
       <c r="J52" s="9" t="str">
@@ -3065,8 +3126,10 @@
 法人番号9900000047001の引継実施ステータスを0（完了）にする。</t>
         </is>
       </c>
-      <c r="H53" s="3" t="str">
-        <v>内容!AV84:AV98</v>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>内容!AV92:AV106</t>
+        </is>
       </c>
       <c r="I53" s="3" t="str"/>
       <c r="J53" s="3" t="str">
@@ -3120,8 +3183,10 @@
 同意書取得組織O0480013の行や他の組織関連項目を誤更新しない。</t>
         </is>
       </c>
-      <c r="H54" s="9" t="str">
-        <v>更新仕様!A108,B238:B242</v>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>更新仕様!A156,B286:B290</t>
+        </is>
       </c>
       <c r="I54" s="9" t="str"/>
       <c r="J54" s="9" t="str">
@@ -3174,8 +3239,10 @@
 存在判定の0／NULL表現はQ05確定後に判定。</t>
         </is>
       </c>
-      <c r="H55" s="3" t="str">
-        <v>内容!AV84:AV85、更新仕様!B145:B149,C296:C297</v>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>内容!AV92:AV93、更新仕様!B193:B197,C344:C345</t>
+        </is>
       </c>
       <c r="I55" s="3" t="str">
         <v>Q05</v>
@@ -3231,8 +3298,10 @@
 存在判定の0／NULL表現はQ05確定後に判定。</t>
         </is>
       </c>
-      <c r="H56" s="9" t="str">
-        <v>内容!AV84:AV85、更新仕様!B145:B149,C296:C297</v>
+      <c r="H56" s="9" t="inlineStr">
+        <is>
+          <t>内容!AV92:AV93、更新仕様!B193:B197,C344:C345</t>
+        </is>
       </c>
       <c r="I56" s="9" t="str">
         <v>Q05</v>
@@ -3285,8 +3354,10 @@
 存在判定の0／NULL表現はQ05確定後に判定。</t>
         </is>
       </c>
-      <c r="H57" s="3" t="str">
-        <v>内容!AV84:AV85、更新仕様!B145:B149,C296:C297</v>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>内容!AV92:AV93、更新仕様!B193:B197,C344:C345</t>
+        </is>
       </c>
       <c r="I57" s="3" t="str">
         <v>Q05</v>
@@ -3339,8 +3410,10 @@
 実施日時は処理時点のDB現在時刻で、観測した時刻区間内となる。</t>
         </is>
       </c>
-      <c r="H58" s="9" t="str">
-        <v>更新仕様!C268:D269,B282:B283</v>
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>更新仕様!C316:D317,B330:B331</t>
+        </is>
       </c>
       <c r="I58" s="9" t="str"/>
       <c r="J58" s="9" t="str">
@@ -3390,8 +3463,10 @@
           <t xml:space="preserve">選定には2026-10-25を使用し、実施日時には2026-10-26の処理時点のNOW()を設定する。</t>
         </is>
       </c>
-      <c r="H59" s="3" t="str">
-        <v>更新仕様!C10:D10,B283</v>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>更新仕様!C10:D10,B331</t>
+        </is>
       </c>
       <c r="I59" s="3" t="str"/>
       <c r="J59" s="3" t="str">
@@ -3442,8 +3517,10 @@
 前提欄の比較用データは状態・実施日時を変更しない。</t>
         </is>
       </c>
-      <c r="H60" s="9" t="str">
-        <v>更新仕様!A273,A301</v>
+      <c r="H60" s="9" t="inlineStr">
+        <is>
+          <t>更新仕様!A321,A349</t>
+        </is>
       </c>
       <c r="I60" s="9" t="str"/>
       <c r="J60" s="9" t="str">
@@ -3495,8 +3572,10 @@
 前提欄の比較用データは状態・実施日時を変更しない。</t>
         </is>
       </c>
-      <c r="H61" s="3" t="str">
-        <v>更新仕様!A273,A301</v>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>更新仕様!A321,A349</t>
+        </is>
       </c>
       <c r="I61" s="3" t="str"/>
       <c r="J61" s="3" t="str">
@@ -3548,8 +3627,10 @@
 前提欄の比較用データは状態・実施日時を変更しない。</t>
         </is>
       </c>
-      <c r="H62" s="9" t="str">
-        <v>更新仕様!A273,A301</v>
+      <c r="H62" s="9" t="inlineStr">
+        <is>
+          <t>更新仕様!A321,A349</t>
+        </is>
       </c>
       <c r="I62" s="9" t="str"/>
       <c r="J62" s="9" t="str">
@@ -3601,8 +3682,10 @@
 前提欄の比較用データは状態・実施日時を変更しない。</t>
         </is>
       </c>
-      <c r="H63" s="3" t="str">
-        <v>更新仕様!A273,A301</v>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>更新仕様!A321,A349</t>
+        </is>
       </c>
       <c r="I63" s="3" t="str"/>
       <c r="J63" s="3" t="str">
@@ -3654,8 +3737,10 @@
 前提欄の比較用データは状態・実施日時を変更しない。</t>
         </is>
       </c>
-      <c r="H64" s="9" t="str">
-        <v>更新仕様!A273,A301</v>
+      <c r="H64" s="9" t="inlineStr">
+        <is>
+          <t>更新仕様!A321,A349</t>
+        </is>
       </c>
       <c r="I64" s="9" t="str"/>
       <c r="J64" s="9" t="str">
@@ -3707,8 +3792,10 @@
 未処理の他予定を誤って完了／エラーにしないことを確認する。</t>
         </is>
       </c>
-      <c r="H65" s="3" t="str">
-        <v>更新仕様!A273,A301</v>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>更新仕様!A321,A349</t>
+        </is>
       </c>
       <c r="I65" s="3" t="str">
         <v>Q07</v>
@@ -4026,8 +4113,10 @@
       <c r="G71" s="3" t="str">
         <v>削除済み行を再作成せず、対象0件として正常終了する。</v>
       </c>
-      <c r="H71" s="3" t="str">
-        <v>内容!AV53:AV55</v>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>内容!AV53:AV55、2026-10-27ユーザー確認</t>
+        </is>
       </c>
       <c r="I71" s="3" t="str"/>
       <c r="J71" s="3" t="str">
@@ -4084,8 +4173,10 @@
 後続法人の継続／停止は設計の終了記述を整理して確定する。</t>
         </is>
       </c>
-      <c r="H72" s="9" t="str">
-        <v>内容!U9,AV84:AV85、フロー図 LOOP</v>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>内容!U9,AV92:AV93、フロー図 LOOP</t>
+        </is>
       </c>
       <c r="I72" s="9" t="str">
         <v>Q05、Q06</v>
@@ -4402,8 +4493,10 @@
       <c r="B78" s="9" t="str">
         <v>例外・トランザクション</v>
       </c>
-      <c r="C78" s="9" t="str">
-        <v>7 過去データ存在確認でException</v>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>8 過去データ存在確認でException</t>
+        </is>
       </c>
       <c r="D78" s="9" t="str">
         <v>異常系</v>
@@ -4462,8 +4555,10 @@
       <c r="B79" s="3" t="str">
         <v>例外・トランザクション</v>
       </c>
-      <c r="C79" s="3" t="str">
-        <v>9 過去データ更新でException</v>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>10 過去データ更新でException</t>
+        </is>
       </c>
       <c r="D79" s="3" t="str">
         <v>異常系</v>
@@ -4522,8 +4617,10 @@
       <c r="B80" s="9" t="str">
         <v>例外・トランザクション</v>
       </c>
-      <c r="C80" s="9" t="str">
-        <v>10 完了更新でException</v>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>11 完了更新でException</t>
+        </is>
       </c>
       <c r="D80" s="9" t="str">
         <v>異常系</v>
@@ -4581,8 +4678,10 @@
       <c r="B81" s="3" t="str">
         <v>例外・トランザクション</v>
       </c>
-      <c r="C81" s="3" t="str">
-        <v>12 エラー状態更新でException</v>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>13 エラー状態更新でException</t>
+        </is>
       </c>
       <c r="D81" s="3" t="str">
         <v>異常系</v>
@@ -4785,8 +4884,10 @@
 文言・レベル・識別項目は実装確認後に確定する。</t>
         </is>
       </c>
-      <c r="H84" s="9" t="str">
-        <v>内容 処理11、計画書 スライド6</v>
+      <c r="H84" s="9" t="inlineStr">
+        <is>
+          <t>内容 処理12、計画書 スライド6</t>
+        </is>
       </c>
       <c r="I84" s="9" t="str">
         <v>Q09</v>
@@ -4798,20 +4899,138 @@
       <c r="L84" s="11" t="str"/>
       <c r="M84" s="10" t="str"/>
       <c r="N84" s="10" t="str"/>
+    </row>
+    <row r="85" ht="230.0" customHeight="1">
+      <c r="A85" s="9">
+        <v>79</v>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>引継元不在・引継先確認</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>引継元不在・引継先登録済み（過去データFALSE）</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>正常系</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="inlineStr">
+        <is>
+          <t>法人番号：9900000079001。
+引継元：組織ID O0790011／担当者ID U0790011（未登録）。
+引継先：組織ID O0790012／担当者ID U0790012（担当者情報マスタに1件登録済み）。
+営業担当引継情報：上記の元→先を1件。予定日2026-10-26、状態1（予定）、引継種別0（個別）、過去データ引継ぎフラグFALSE。登録・更新日時2026-10-26 00:30:00、実施日時NULL。
+月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・建物マスタ・CN対策実施申込情報・建物情報：上記法人・引継元組織で各1件。建物マスタは同意書取得組織、他7表は組織IDに引継元組織を設定。</t>
+        </is>
+      </c>
+      <c r="F85" s="9" t="inlineStr">
+        <is>
+          <t>① --case 79でテストデータを準備し、引継情報・登録済み担当者・過去データ全行を保存する。
+② リポジトリのルートで実行する。
+python -m cndx_corp_batch.entrypoints.sales_user_handover_batch --batch-date 2026-10-26
+③ 保存した各行と実行後のDBを比較する。担当者マスタを更新・削除しないこと、フラグに応じた過去データ処理と完了更新を確認する。</t>
+        </is>
+      </c>
+      <c r="G85" s="9" t="inlineStr">
+        <is>
+          <t>法人番号9900000079001の営業担当引継情報1件を残し、状態0（完了）へ更新する。実施日時は処理前後のDB時刻の範囲内。
+担当者情報マスタのO0790012／U0790012は全項目を保持し、元担当者は作成しない。
+月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・建物マスタ・CN対策実施申込情報・建物情報は各1件のまま、全項目を保持する。過去データの存在確認・更新は呼び出さない。</t>
+        </is>
+      </c>
+      <c r="H85" s="9" t="inlineStr">
+        <is>
+          <t>内容!AV60:AV75、更新仕様!A125、追加要件画像（2026-10-26指示）、2026-10-27ユーザー確認</t>
+        </is>
+      </c>
+      <c r="I85" s="9"/>
+      <c r="J85" s="9" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="K85" s="10"/>
+      <c r="L85" s="11"/>
+      <c r="M85" s="10"/>
+      <c r="N85" s="10"/>
+    </row>
+    <row r="86" ht="230.0" customHeight="1">
+      <c r="A86" s="9">
+        <v>80</v>
+      </c>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>引継元不在・引継先確認</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>引継元不在・引継先登録済み（過去データTRUE）</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>正常系</t>
+        </is>
+      </c>
+      <c r="E86" s="9" t="inlineStr">
+        <is>
+          <t>法人番号：9900000080001。
+引継元：組織ID O0800011／担当者ID U0800011（未登録）。
+引継先：組織ID O0800012／担当者ID U0800012（担当者情報マスタに1件登録済み）。
+営業担当引継情報：上記の元→先を1件。予定日2026-10-26、状態1（予定）、引継種別0（個別）、過去データ引継ぎフラグTRUE。登録・更新日時2026-10-26 00:30:00、実施日時NULL。
+月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・建物マスタ・CN対策実施申込情報・建物情報：上記法人・引継元組織で各1件。建物マスタは同意書取得組織、他7表は組織IDに引継元組織を設定。</t>
+        </is>
+      </c>
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>① --case 80でテストデータを準備し、引継情報・登録済み担当者・過去データ全行を保存する。
+② リポジトリのルートで実行する。
+python -m cndx_corp_batch.entrypoints.sales_user_handover_batch --batch-date 2026-10-26
+③ 保存した各行と実行後のDBを比較する。担当者マスタを更新・削除しないこと、フラグに応じた過去データ処理と完了更新を確認する。</t>
+        </is>
+      </c>
+      <c r="G86" s="9" t="inlineStr">
+        <is>
+          <t>法人番号9900000080001の営業担当引継情報1件を残し、状態0（完了）へ更新する。実施日時は処理前後のDB時刻の範囲内。
+担当者情報マスタのO0800012／U0800012は全項目を保持し、元担当者は作成しない。
+月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・建物マスタ・CN対策実施申込情報・建物情報は各1件のまま、引継元組織O0800011を引継先組織O0800012へ更新する。建物マスタは同意書取得組織、他7表は組織IDを更新し、それ以外の項目を保持する。</t>
+        </is>
+      </c>
+      <c r="H86" s="9" t="inlineStr">
+        <is>
+          <t>内容!AV60:AV75、更新仕様!A125、追加要件画像（2026-10-26指示）、2026-10-27ユーザー確認</t>
+        </is>
+      </c>
+      <c r="I86" s="9"/>
+      <c r="J86" s="9" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="K86" s="10"/>
+      <c r="L86" s="11"/>
+      <c r="M86" s="10"/>
+      <c r="N86" s="10"/>
     </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A3:N3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J7:J84">
+  <conditionalFormatting sqref="J7:J86">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="仕様確認待ち"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K7:K84">
+  <conditionalFormatting sqref="K7:K86">
     <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="不合格"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="K7:K84">
+    <dataValidation type="list" sqref="K7:K86">
       <formula1>"合格,不合格,保留"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4966,7 +5185,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="46" customHeight="1">
+    <row r="14" ht="92.0" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">担当者情報マスタの準備</t>
@@ -4974,9 +5193,10 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">各ケースの前提欄に記載した法人・組織・担当者を登録する。「未登録」と記載した担当者は登録しない。
+          <t>各ケースの前提欄に記載した法人・組織・担当者を登録する。「未登録」と記載した担当者は登録しない。
 法人の親データと、必要な組織・利用者等の参照マスタも検証DBに用意する。
-準備PGは参照マスタを作成しない。既存のテスト用IDを使う場合は設定JSONと対応させる。</t>
+準備PGは参照マスタを作成しない。既存のテスト用IDを使う場合は設定JSONと対応させる。
+追加要件画像を優先：元が不在でも同じ法人に先がいれば、担当者を変更せず過去データフラグ判定へ進む。FALSEは過去データを保持して完了、TRUEは過去データを引き継ぐ。両方不在なら対象引継情報を削除し、次法人へ進む。</t>
         </is>
       </c>
     </row>
@@ -5257,313 +5477,341 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr>
-    <x:tabColor rgb="FF305878"/>
-  </x:sheetPr>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="8.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="50" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="53.75" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="26.25" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="11.25" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="41.25" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="3"/>
-      <x:c r="B1" s="3"/>
-      <x:c r="C1" s="3"/>
-      <x:c r="D1" s="3"/>
-      <x:c r="E1" s="3"/>
-      <x:c r="F1" s="3"/>
-      <x:c r="G1" s="3"/>
-    </x:row>
-    <x:row r="2" ht="27" customHeight="1">
-      <x:c r="A2" s="4" t="str">
-        <x:v>仕様確認事項</x:v>
-      </x:c>
-      <x:c r="B2" s="4"/>
-      <x:c r="C2" s="4"/>
-      <x:c r="D2" s="4"/>
-      <x:c r="E2" s="4"/>
-      <x:c r="F2" s="4"/>
-      <x:c r="G2" s="4"/>
-    </x:row>
-    <x:row r="3" ht="32" customHeight="1">
-      <x:c r="A3" s="3" t="str">
-        <x:v>設計書の矛盾・不足を記録。回答後に関連ケースの予想結果を確定する。</x:v>
-      </x:c>
-      <x:c r="B3" s="3"/>
-      <x:c r="C3" s="3"/>
-      <x:c r="D3" s="3"/>
-      <x:c r="E3" s="3"/>
-      <x:c r="F3" s="3"/>
-      <x:c r="G3" s="3"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="3"/>
-      <x:c r="B4" s="3"/>
-      <x:c r="C4" s="3"/>
-      <x:c r="D4" s="3"/>
-      <x:c r="E4" s="3"/>
-      <x:c r="F4" s="3"/>
-      <x:c r="G4" s="3"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="3"/>
-      <x:c r="B5" s="3"/>
-      <x:c r="C5" s="3"/>
-      <x:c r="D5" s="3"/>
-      <x:c r="E5" s="3"/>
-      <x:c r="F5" s="3"/>
-      <x:c r="G5" s="3"/>
-    </x:row>
-    <x:row r="6" ht="32" customHeight="1">
-      <x:c r="A6" s="8" t="str">
-        <x:v>ID</x:v>
-      </x:c>
-      <x:c r="B6" s="8" t="str">
-        <x:v>論点</x:v>
-      </x:c>
-      <x:c r="C6" s="8" t="str">
-        <x:v>設計書の記載</x:v>
-      </x:c>
-      <x:c r="D6" s="8" t="str">
-        <x:v>確認内容・扱い</x:v>
-      </x:c>
-      <x:c r="E6" s="8" t="str">
-        <x:v>関連項番</x:v>
-      </x:c>
-      <x:c r="F6" s="8" t="str">
-        <x:v>確認状況</x:v>
-      </x:c>
-      <x:c r="G6" s="8" t="str">
-        <x:v>回答・確定内容</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="42" customHeight="1">
-      <x:c r="A7" s="3" t="str">
-        <x:v>Q01</x:v>
-      </x:c>
-      <x:c r="B7" s="3" t="str">
-        <x:v>登録締切</x:v>
-      </x:c>
-      <x:c r="C7" s="3" t="str">
-        <x:v>概要B28:B30は起動日0:59まで。更新仕様A26/B42:B43は状態と予定日だけ。</x:v>
-      </x:c>
-      <x:c r="D7" s="3" t="str">
-        <x:v>締切の秒精度、引数指定日との関係、開始後登録データの扱いと抽出条件を確定する。</x:v>
-      </x:c>
-      <x:c r="E7" s="3" t="str">
-        <x:v>16, 17, 18, 19</x:v>
-      </x:c>
-      <x:c r="F7" s="10" t="str">
-        <x:v>未確認</x:v>
-      </x:c>
-      <x:c r="G7" s="10" t="str"/>
-    </x:row>
-    <x:row r="8" ht="42" customHeight="1">
-      <x:c r="A8" s="9" t="str">
-        <x:v>Q02</x:v>
-      </x:c>
-      <x:c r="B8" s="9" t="str">
-        <x:v>担当者の組織ID</x:v>
-      </x:c>
-      <x:c r="C8" s="9" t="str">
-        <x:v>内容AV45は組織ID更新。更新仕様A50:C67では担当者ユーザーIDだけ更新。</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="str">
-        <x:v>担当者情報マスタの実カラムと組織更新要否を統一する。</x:v>
-      </x:c>
-      <x:c r="E8" s="9" t="str">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F8" s="10" t="str">
-        <x:v>未確認</x:v>
-      </x:c>
-      <x:c r="G8" s="10" t="str"/>
-    </x:row>
-    <x:row r="9" ht="42" customHeight="1">
-      <x:c r="A9" s="3" t="str">
-        <x:v>Q03</x:v>
-      </x:c>
-      <x:c r="B9" s="3" t="str">
-        <x:v>引継先担当者登録済み</x:v>
-      </x:c>
-      <x:c r="C9" s="3" t="str">
-        <x:v>概要B13:B14は引継元担当者削除。詳細フローと更新仕様に重複時分岐がない。</x:v>
-      </x:c>
-      <x:c r="D9" s="3" t="str">
-        <x:v>同一法人に引継先が存在する場合の削除条件と後続処理を定義する。</x:v>
-      </x:c>
-      <x:c r="E9" s="3" t="str">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F9" s="10" t="str">
-        <x:v>未確認</x:v>
-      </x:c>
-      <x:c r="G9" s="10" t="str"/>
-    </x:row>
-    <x:row r="10" ht="42" customHeight="1">
-      <x:c r="A10" s="9" t="str">
-        <x:v>Q04</x:v>
-      </x:c>
-      <x:c r="B10" s="9" t="str">
-        <x:v>引継元不在と削除範囲</x:v>
-      </x:c>
-      <x:c r="C10" s="9" t="str">
-        <x:v>更新仕様A79/B88:B90は全法人のユーザーIDを検索し、DELETEに対象行のキーがない。</x:v>
-      </x:c>
-      <x:c r="D10" s="9" t="str">
-        <x:v>法人単位の存在判定、対象予定を1件に絞る削除キー、削除後の進路を明示する。全件削除の期待値にはしない。</x:v>
-      </x:c>
-      <x:c r="E10" s="9" t="str">
-        <x:v>26, 27</x:v>
-      </x:c>
-      <x:c r="F10" s="10" t="str">
-        <x:v>未確認</x:v>
-      </x:c>
-      <x:c r="G10" s="10" t="str"/>
-    </x:row>
-    <x:row r="11" ht="42" customHeight="1">
-      <x:c r="A11" s="3" t="str">
-        <x:v>Q05</x:v>
-      </x:c>
-      <x:c r="B11" s="3" t="str">
-        <x:v>建物マスタ未存在の表現</x:v>
-      </x:c>
-      <x:c r="C11" s="3" t="str">
-        <x:v>内容AV76/AV84はNULLを判定。更新仕様B145:B149のEXISTSは0/1を返す。</x:v>
-      </x:c>
-      <x:c r="D11" s="3" t="str">
-        <x:v>未存在を0として判定するかを統一する。業務エラーはロールバックなしの規定を維持する。</x:v>
-      </x:c>
-      <x:c r="E11" s="3" t="str">
-        <x:v>49, 50, 51, 66</x:v>
-      </x:c>
-      <x:c r="F11" s="10" t="str">
-        <x:v>未確認</x:v>
-      </x:c>
-      <x:c r="G11" s="10" t="str"/>
-    </x:row>
-    <x:row r="12" ht="42" customHeight="1">
-      <x:c r="A12" s="9" t="str">
-        <x:v>Q06</x:v>
-      </x:c>
-      <x:c r="B12" s="9" t="str">
-        <x:v>例外時の終了・コミット境界</x:v>
-      </x:c>
-      <x:c r="C12" s="9" t="str">
-        <x:v>内容U9は「11.終了」だが実際は13.終了。図には処理5/9/10/12付近に複数のCOMMITがある。</x:v>
-      </x:c>
-      <x:c r="D12" s="9" t="str">
-        <x:v>各トランザクションの開始・終了、Exception時の状態3記録、後続法人の継続可否を確定する。</x:v>
-      </x:c>
-      <x:c r="E12" s="9" t="str">
-        <x:v>66, 67, 68, 69, 70, 71, 72, 73, 74, 75, 76</x:v>
-      </x:c>
-      <x:c r="F12" s="10" t="str">
-        <x:v>未確認</x:v>
-      </x:c>
-      <x:c r="G12" s="10" t="str"/>
-    </x:row>
-    <x:row r="13" ht="42" customHeight="1">
-      <x:c r="A13" s="3" t="str">
-        <x:v>Q07</x:v>
-      </x:c>
-      <x:c r="B13" s="3" t="str">
-        <x:v>状態更新の対象キー</x:v>
-      </x:c>
-      <x:c r="C13" s="3" t="str">
-        <x:v>更新仕様A273/A301に元・先担当者IDがない。</x:v>
-      </x:c>
-      <x:c r="D13" s="3" t="str">
-        <x:v>同一法人・同一組織間に複数予定があり得るか確認し、必要な一意キーを定義する。</x:v>
-      </x:c>
-      <x:c r="E13" s="3" t="str">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F13" s="10" t="str">
-        <x:v>未確認</x:v>
-      </x:c>
-      <x:c r="G13" s="10" t="str"/>
-    </x:row>
-    <x:row r="14" ht="42" customHeight="1">
-      <x:c r="A14" s="9" t="str">
-        <x:v>Q08</x:v>
-      </x:c>
-      <x:c r="B14" s="9" t="str">
-        <x:v>NULLと入力制約</x:v>
-      </x:c>
-      <x:c r="C14" s="9" t="str">
-        <x:v>入力項目チェック仕様説明書の図形は「入力項目チェックなし」。フラグNULLの扱いは未記載。</x:v>
-      </x:c>
-      <x:c r="D14" s="9" t="str">
-        <x:v>DBのNULL許容とフラグの扱いを確認する。日付不正などの追加バリデーション仕様を独自に作らない。</x:v>
-      </x:c>
-      <x:c r="E14" s="9" t="str">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F14" s="10" t="str">
-        <x:v>未確認</x:v>
-      </x:c>
-      <x:c r="G14" s="10" t="str"/>
-    </x:row>
-    <x:row r="15" ht="42" customHeight="1">
-      <x:c r="A15" s="3" t="str">
-        <x:v>Q09</x:v>
-      </x:c>
-      <x:c r="B15" s="3" t="str">
-        <x:v>ログ仕様</x:v>
-      </x:c>
-      <x:c r="C15" s="3" t="str">
-        <x:v>計画書は正常／異常ログの検証を要求。バッチ設計に具体的な文言・レベルはない。</x:v>
-      </x:c>
-      <x:c r="D15" s="3" t="str">
-        <x:v>実装のログ仕様を確認して期待結果を具体化する。</x:v>
-      </x:c>
-      <x:c r="E15" s="3" t="str">
-        <x:v>77, 78</x:v>
-      </x:c>
-      <x:c r="F15" s="10" t="str">
-        <x:v>未確認</x:v>
-      </x:c>
-      <x:c r="G15" s="10" t="str"/>
-    </x:row>
-    <x:row r="16" ht="56" customHeight="1">
-      <x:c r="A16" s="9" t="str">
-        <x:v>Q10</x:v>
-      </x:c>
-      <x:c r="B16" s="9" t="str">
-        <x:v>SQL例の誤記と名称差</x:v>
-      </x:c>
-      <x:c r="C16" s="9" t="str">
-        <x:v>更新仕様B202の「年度別別」、B230の途中セミコロン、B240の別テーブル名。概要図と更新仕様でエネルギー情報名に「集計」の差がある。</x:v>
-      </x:c>
-      <x:c r="D16" s="9" t="str">
-        <x:v>実装時は対象テーブル・条件の定義と照合する。ケースは更新仕様の論理テーブル名を採用し、SQL例の構文誤りを正解としない。</x:v>
-      </x:c>
-      <x:c r="E16" s="9" t="str">
-        <x:v>関連SQL実装時に確認</x:v>
-      </x:c>
-      <x:c r="F16" s="10" t="str">
-        <x:v>未確認</x:v>
-      </x:c>
-      <x:c r="G16" s="10" t="str"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A2:G2"/>
-    <x:mergeCell ref="A3:G3"/>
-  </x:mergeCells>
-  <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="F7:F16">
-      <x:formula1>"未確認,確認中,確定"</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF305878"/>
+  </sheetPr>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="8.130000114440918" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="50" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="53.75" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="26.25" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="11.25" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="41.25" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" ht="27" customHeight="1">
+      <c r="A2" s="4" t="str">
+        <v>仕様確認事項</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="3" t="str">
+        <v>設計書の矛盾・不足を記録。回答後に関連ケースの予想結果を確定する。</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="8" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B6" s="8" t="str">
+        <v>論点</v>
+      </c>
+      <c r="C6" s="8" t="str">
+        <v>設計書の記載</v>
+      </c>
+      <c r="D6" s="8" t="str">
+        <v>確認内容・扱い</v>
+      </c>
+      <c r="E6" s="8" t="str">
+        <v>関連項番</v>
+      </c>
+      <c r="F6" s="8" t="str">
+        <v>確認状況</v>
+      </c>
+      <c r="G6" s="8" t="str">
+        <v>回答・確定内容</v>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="3" t="str">
+        <v>Q01</v>
+      </c>
+      <c r="B7" s="3" t="str">
+        <v>登録締切</v>
+      </c>
+      <c r="C7" s="3" t="str">
+        <v>概要B28:B30は起動日0:59まで。更新仕様A26/B42:B43は状態と予定日だけ。</v>
+      </c>
+      <c r="D7" s="3" t="str">
+        <v>締切の秒精度、引数指定日との関係、開始後登録データの扱いと抽出条件を確定する。</v>
+      </c>
+      <c r="E7" s="3" t="str">
+        <v>16, 17, 18, 19</v>
+      </c>
+      <c r="F7" s="10" t="str">
+        <v>未確認</v>
+      </c>
+      <c r="G7" s="10" t="str"/>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="9" t="str">
+        <v>Q02</v>
+      </c>
+      <c r="B8" s="9" t="str">
+        <v>担当者の組織ID</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>内容AV45は組織ID更新。更新仕様A74:C91では担当者ユーザーIDだけ更新。</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="str">
+        <v>担当者情報マスタの実カラムと組織更新要否を統一する。</v>
+      </c>
+      <c r="E8" s="9" t="str">
+        <v>23</v>
+      </c>
+      <c r="F8" s="10" t="str">
+        <v>未確認</v>
+      </c>
+      <c r="G8" s="10" t="str"/>
+    </row>
+    <row r="9" ht="118.0" customHeight="1">
+      <c r="A9" s="3" t="str">
+        <v>Q03</v>
+      </c>
+      <c r="B9" s="3" t="str">
+        <v>引継先担当者登録済み</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>概要B13:B14は引継元担当者削除。改訂で元担当者不在時の先担当者確認（処理6）が追加されたが、元・先とも存在する場合の詳細分岐は未記載。</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="str">
+        <v>同一法人に引継先が存在する場合の削除条件と後続処理を定義する。</v>
+      </c>
+      <c r="E9" s="3" t="str">
+        <v>24</v>
+      </c>
+      <c r="F9" s="10" t="str">
+        <v>未確認</v>
+      </c>
+      <c r="G9" s="10" t="str"/>
+    </row>
+    <row r="10" ht="118.0" customHeight="1">
+      <c r="A10" s="9" t="str">
+        <v>Q04</v>
+      </c>
+      <c r="B10" s="9" t="str">
+        <v>引継元不在と削除範囲</v>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>改訂の元担当者確認は法人番号を条件に含む（更新仕様A54）。削除条件A103/B112:B114は全法人のユーザーIDを検索し、DELETEに対象行のキーがない。</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>法人単位の存在判定と、元不在時は同じ法人の先を確認して分岐することは確認済み。対象予定を1件に絞る削除キーを設計SQLにも明示する必要がある。全件削除の期待値にはしない。</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>25, 26, 27, 65, 79, 80</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>確認中</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-27ユーザー指示で追加要件画像を優先：元が不在でも同じ法人に先が存在すれば、担当者を変更せず過去データ引継ぎフラグの判定へ進む。両方不在なら対象引継情報を削除し、次法人へ進む。削除キーの設計SQLへの明記は引き続き確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="118.0" customHeight="1">
+      <c r="A11" s="3" t="str">
+        <v>Q05</v>
+      </c>
+      <c r="B11" s="3" t="str">
+        <v>建物マスタ未存在の表現</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>内容AV84/AV92はNULLを判定。更新仕様B193:B197のEXISTSは0/1を返す。</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="str">
+        <v>未存在を0として判定するかを統一する。業務エラーはロールバックなしの規定を維持する。</v>
+      </c>
+      <c r="E11" s="3" t="str">
+        <v>49, 50, 51, 66</v>
+      </c>
+      <c r="F11" s="10" t="str">
+        <v>未確認</v>
+      </c>
+      <c r="G11" s="10" t="str"/>
+    </row>
+    <row r="12" ht="118.0" customHeight="1">
+      <c r="A12" s="9" t="str">
+        <v>Q06</v>
+      </c>
+      <c r="B12" s="9" t="str">
+        <v>例外時の終了・コミット境界</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>内容U9は「11.終了」だが改訂後の終了は14。図には処理5/10/11/13付近に複数のCOMMITがある。</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="str">
+        <v>各トランザクションの開始・終了、Exception時の状態3記録、後続法人の継続可否を確定する。</v>
+      </c>
+      <c r="E12" s="9" t="str">
+        <v>66, 67, 68, 69, 70, 71, 72, 73, 74, 75, 76</v>
+      </c>
+      <c r="F12" s="10" t="str">
+        <v>未確認</v>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-27確認済み：元・先とも不在の場合の「14.終了へ」は該当法人だけの終了で、次の法人を処理する。この回答はException時の継続可否・コミット境界を確定するものではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="3" t="str">
+        <v>Q07</v>
+      </c>
+      <c r="B13" s="3" t="str">
+        <v>状態更新の対象キー</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>更新仕様A321/A349に元・先担当者IDがない。</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="str">
+        <v>同一法人・同一組織間に複数予定があり得るか確認し、必要な一意キーを定義する。</v>
+      </c>
+      <c r="E13" s="3" t="str">
+        <v>59</v>
+      </c>
+      <c r="F13" s="10" t="str">
+        <v>未確認</v>
+      </c>
+      <c r="G13" s="10" t="str"/>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="9" t="str">
+        <v>Q08</v>
+      </c>
+      <c r="B14" s="9" t="str">
+        <v>NULLと入力制約</v>
+      </c>
+      <c r="C14" s="9" t="str">
+        <v>入力項目チェック仕様説明書の図形は「入力項目チェックなし」。フラグNULLの扱いは未記載。</v>
+      </c>
+      <c r="D14" s="9" t="str">
+        <v>DBのNULL許容とフラグの扱いを確認する。日付不正などの追加バリデーション仕様を独自に作らない。</v>
+      </c>
+      <c r="E14" s="9" t="str">
+        <v>32</v>
+      </c>
+      <c r="F14" s="10" t="str">
+        <v>未確認</v>
+      </c>
+      <c r="G14" s="10" t="str"/>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="3" t="str">
+        <v>Q09</v>
+      </c>
+      <c r="B15" s="3" t="str">
+        <v>ログ仕様</v>
+      </c>
+      <c r="C15" s="3" t="str">
+        <v>計画書は正常／異常ログの検証を要求。バッチ設計に具体的な文言・レベルはない。</v>
+      </c>
+      <c r="D15" s="3" t="str">
+        <v>実装のログ仕様を確認して期待結果を具体化する。</v>
+      </c>
+      <c r="E15" s="3" t="str">
+        <v>77, 78</v>
+      </c>
+      <c r="F15" s="10" t="str">
+        <v>未確認</v>
+      </c>
+      <c r="G15" s="10" t="str"/>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="A16" s="9" t="str">
+        <v>Q10</v>
+      </c>
+      <c r="B16" s="9" t="str">
+        <v>SQL例の誤記と名称差</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>更新仕様B250の「年度別別」、B278の途中セミコロン、B288の別テーブル名。概要図と更新仕様でエネルギー情報名に「集計」の差がある。</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="str">
+        <v>実装時は対象テーブル・条件の定義と照合する。ケースは更新仕様の論理テーブル名を採用し、SQL例の構文誤りを正解としない。</v>
+      </c>
+      <c r="E16" s="9" t="str">
+        <v>関連SQL実装時に確認</v>
+      </c>
+      <c r="F16" s="10" t="str">
+        <v>未確認</v>
+      </c>
+      <c r="G16" s="10" t="str"/>
+    </row>
+  </sheetData>
+  <mergeCells>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="F7:F16">
+      <formula1>"未確認,確認中,確定"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/PG2-1-01_単体テストケース・結果一覧表_担当者引継ぎ実行.xlsx
+++ b/docs/PG2-1-01_単体テストケース・結果一覧表_担当者引継ぎ実行.xlsx
@@ -1550,8 +1550,9 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">法人番号 9900000020001/担当者ID U0200011の担当者ユーザーIDをU0200012へ変更する。
-元担当者の行を余分に残さず、他の担当者を変更しない。</t>
+          <t>法人番号 9900000020001/担当者ID U0200011の担当者ユーザーIDをU0200012へ変更する。
+元担当者の行を余分に残さず、他の担当者を変更しない。
+担当者情報マスタの組織IDはO0200011のまま保持する。</t>
         </is>
       </c>
       <c r="H26" s="9" t="inlineStr">
@@ -1604,7 +1605,8 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">法人番号 9900000021001/担当者ID U0210011だけが法人番号 9900000021001/担当者ID U0210012となり、法人番号 9900000021002/担当者ID U0210011は変更しない。</t>
+          <t>法人番号 9900000021001/担当者ID U0210011だけが法人番号 9900000021001/担当者ID U0210012となり、法人番号 9900000021002/担当者ID U0210011は変更しない。
+担当者情報マスタの組織IDはO0210011のまま保持する。</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
@@ -1657,7 +1659,8 @@
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">法人番号 9900000022001/担当者ID U0220011だけが法人番号 9900000022001/担当者ID U0220012となり、法人番号 9900000022001/担当者ID U0220013は変更しない。</t>
+          <t>法人番号 9900000022001/担当者ID U0220011だけが法人番号 9900000022001/担当者ID U0220012となり、法人番号 9900000022001/担当者ID U0220013は変更しない。
+担当者情報マスタの組織IDはO0220011のまま保持する。</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
@@ -1681,8 +1684,10 @@
       <c r="B29" s="3" t="str">
         <v>担当者更新</v>
       </c>
-      <c r="C29" s="3" t="str">
-        <v>組織IDの更新有無</v>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>担当者の組織IDを更新しない</t>
+        </is>
       </c>
       <c r="D29" s="3" t="str">
         <v>正常系</v>
@@ -1709,20 +1714,23 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">本文に従う案は担当者組織を組織ID O0230012へ変更する。
-更新仕様のSET句には組織IDがないため、正しい項目と要否の確定後に判定する。</t>
+          <t>法人番号9900000023001の担当者情報マスタは、担当者ユーザーIDをU0230011からU0230012へ変更する。
+組織IDはO0230011を保持し、引継先組織O0230012へ変更しない。法人番号およびその他の項目も保持する。
+営業担当引継情報は状態0（完了）に更新し、実施日時を設定する。</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>内容!AV45:AV46、更新仕様!A74:C91</t>
+          <t>内容!AV45:AV46、更新仕様!A74:C91、2026-10-28 Q02回答（更新仕様を正とする）</t>
         </is>
       </c>
       <c r="I29" s="3" t="str">
         <v>Q02</v>
       </c>
-      <c r="J29" s="3" t="str">
-        <v>仕様確認待ち</v>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
       </c>
       <c r="K29" s="10" t="str"/>
       <c r="L29" s="11" t="str"/>
@@ -1993,8 +2001,9 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者を更新し、過去データの存在確認・建物マスタ不在判定・組織更新を実施しない。
-8テーブル（月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・建物マスタ・CN対策実施申込情報・建物情報）の組織を組織ID O0280011のまま保持し、予定を完了0にする。</t>
+          <t>担当者を更新し、過去データの存在確認・建物マスタ不在判定・組織更新を実施しない。
+8テーブル（月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・建物マスタ・CN対策実施申込情報・建物情報）の組織を組織ID O0280011のまま保持し、予定を完了0にする。
+担当者情報マスタの組織IDはO0280011のまま保持する。</t>
         </is>
       </c>
       <c r="H34" s="9" t="inlineStr">
@@ -2046,8 +2055,9 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">建物マスタ存在チェックを行わず担当者を更新し、完了0にする。
-登録エラー3にしない。</t>
+          <t>建物マスタ存在チェックを行わず担当者を更新し、完了0にする。
+登録エラー3にしない。
+担当者情報マスタの組織IDはO0290011のまま保持する。</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -2100,9 +2110,10 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・CN対策実施申込情報・建物情報の組織IDをO0300012へ変更する。
+          <t>月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・CN対策実施申込情報・建物情報の組織IDをO0300012へ変更する。
 建物マスタは同意書取得組織をO0300012へ変更する。
-法人番号9900000030001の担当者をU0300012へ更新し、引継実施ステータス0（完了）と実施日時を確認する。</t>
+法人番号9900000030001の担当者をU0300012へ更新し、引継実施ステータス0（完了）と実施日時を確認する。
+担当者情報マスタの組織IDはO0300011のまま保持する。</t>
         </is>
       </c>
       <c r="H36" s="9" t="inlineStr">
@@ -3903,9 +3914,10 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">法人番号9900000061001・9900000061002・9900000061003を各1回処理し、担当者IDをU0610012へ変更して引継実施ステータスを0（完了）にする。
+          <t>法人番号9900000061001・9900000061002・9900000061003を各1回処理し、担当者IDをU0610012へ変更して引継実施ステータスを0（完了）にする。
 法人番号9900000061001・9900000061003の月別建物エネルギー情報・年度別建物エネルギー情報・月別法人エネルギー情報・年度別法人エネルギー情報・レポート格納情報・建物マスタ・CN対策実施申込情報・建物情報を引継先組織O0610012へ変更する（建物マスタは同意書取得組織を更新）。
-法人番号9900000061002の過去データは組織O0610011のまま保持する。</t>
+法人番号9900000061002の過去データは組織O0610011のまま保持する。
+担当者情報マスタの組織IDはO0610011のまま保持する。</t>
         </is>
       </c>
       <c r="H67" s="3" t="str">
@@ -3955,9 +3967,10 @@
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">300件すべてを重複・欠落なく完了する。
+          <t>300件すべてを重複・欠落なく完了する。
 担当者更新数・完了数が300件と一致する。
-実行時間は記録のみとし、性能合否は定めない。</t>
+実行時間は記録のみとし、性能合否は定めない。
+担当者情報マスタの組織IDはO0620011のまま保持する。</t>
         </is>
       </c>
       <c r="H68" s="9" t="str">
@@ -5095,8 +5108,9 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者引継ぎ実行バッチ（BLMMGMGHANDOVER／処理機能ID：LMMGMG06-01）。
-法人の担当者を引継元から引継先へ変更し、指定された場合は過去データの組織も変更する。</t>
+          <t>担当者引継ぎ実行バッチ（BLMMGMGHANDOVER／処理機能ID：LMMGMG06-01）。
+法人の担当者を引継元から引継先へ変更し、指定された場合は過去データの組織も変更する。
+担当者情報マスタの更新は担当者ユーザーIDのみ。組織IDは保持する（Q02確定）。</t>
         </is>
       </c>
     </row>
@@ -5284,7 +5298,7 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">組織を変更するケースでは、変更前後の行を比較し、法人番号・建物ID・年月・電力量・レポート情報が変わらないことを確認する。
+          <t>過去データの組織を変更するケースでは、変更前後の行を比較し、法人番号・建物ID・年月・電力量・レポート情報が変わらないことを確認する。
 更新対象外の行と、テーブルの件数も確認する（担当者削除など、件数が変わるケースは期待結果に従う）。
 更新者等の監査項目は仕様未定のため、独自の期待値を追加しない。</t>
         </is>
@@ -5597,16 +5611,24 @@
           <t>内容AV45は組織ID更新。更新仕様A74:C91では担当者ユーザーIDだけ更新。</t>
         </is>
       </c>
-      <c r="D8" s="9" t="str">
-        <v>担当者情報マスタの実カラムと組織更新要否を統一する。</v>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>更新仕様を正とし、担当者情報マスタは担当者ユーザーIDだけを更新する。組織IDは更新前の値を保持する。</t>
+        </is>
       </c>
       <c r="E8" s="9" t="str">
         <v>23</v>
       </c>
-      <c r="F8" s="10" t="str">
-        <v>未確認</v>
-      </c>
-      <c r="G8" s="10" t="str"/>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-28ユーザー回答：更新仕様が正しいため、担当者情報マスタの組織IDは更新しない。過去データの組織更新は従来どおりフラグに従う。</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="118.0" customHeight="1">
       <c r="A9" s="3" t="str">
